--- a/distinta_vuota.xlsx
+++ b/distinta_vuota.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Server\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CF3A49-737B-4A54-9476-6BFBECA22180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61278403-7ACD-471D-B6D3-51B9A05AB0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BF18F4E-3627-49D6-B6A0-5A92BEB215F1}"/>
+    <workbookView xWindow="2730" yWindow="1635" windowWidth="11820" windowHeight="14565" xr2:uid="{7BF18F4E-3627-49D6-B6A0-5A92BEB215F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Convocati" sheetId="2" r:id="rId1"/>
@@ -34,15 +34,9 @@
     <t xml:space="preserve"> Zenith Prato S.S.D.R.L.</t>
   </si>
   <si>
-    <t>U10 PULCINI 2016</t>
-  </si>
-  <si>
     <t>Sede: Via del Purgatorio 81/a - 0574633593</t>
   </si>
   <si>
-    <t>Stagione sportiva 2025/2026</t>
-  </si>
-  <si>
     <t>Distinta dei giocatori partecipanti alla gara:</t>
   </si>
   <si>
@@ -107,6 +101,12 @@
   </si>
   <si>
     <t>Campionato</t>
+  </si>
+  <si>
+    <t>Stagione sportiva 2026/2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Primi calci 2019</t>
   </si>
 </sst>
 </file>
@@ -378,12 +378,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -391,6 +385,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,14 +719,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="21"/>
       <c r="D1" s="21"/>
       <c r="E1" s="21"/>
       <c r="F1" s="22"/>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="33" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="21"/>
@@ -735,28 +735,28 @@
       <c r="K1" s="22"/>
     </row>
     <row r="2" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="32"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="32"/>
     </row>
     <row r="3" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="34"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
     </row>
     <row r="4" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="23"/>
@@ -771,15 +771,15 @@
       <c r="K4" s="25"/>
     </row>
     <row r="5" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
-        <v>2</v>
+      <c r="B5" s="34" t="s">
+        <v>26</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16"/>
       <c r="G5" s="19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="15"/>
@@ -787,15 +787,15 @@
       <c r="K5" s="16"/>
     </row>
     <row r="6" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
-        <v>4</v>
+      <c r="B6" s="35" t="s">
+        <v>25</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
       <c r="G6" s="19" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -804,14 +804,14 @@
     </row>
     <row r="7" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="29" t="s">
-        <v>24</v>
+      <c r="G7" s="34" t="s">
+        <v>22</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
@@ -819,13 +819,13 @@
       <c r="K7" s="16"/>
     </row>
     <row r="8" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="30"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
       <c r="G8" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -839,7 +839,7 @@
       <c r="E9" s="15"/>
       <c r="F9" s="16"/>
       <c r="G9" s="19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
@@ -860,34 +860,34 @@
     </row>
     <row r="11" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
@@ -1204,26 +1204,26 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C38" s="27"/>
       <c r="D38" s="26" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E38" s="28"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I38" s="27"/>
       <c r="J38" s="13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -1350,14 +1350,14 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
       <c r="F49" s="16"/>
       <c r="G49" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
